--- a/data/trans_orig/P24C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2007 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47341</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68672</t>
+          <t>68398</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29210</t>
+          <t>28693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46430</t>
+          <t>47151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>82555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110666</t>
+          <t>110961</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43475</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>47108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75298</t>
+          <t>72854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32647</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40057</t>
+          <t>42604</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>22,95%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74233</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103177</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>37580</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>58504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120640</t>
+          <t>120337</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155094</t>
+          <t>155530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41589</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67557</t>
+          <t>68093</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49855</t>
+          <t>49129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77735</t>
+          <t>77613</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>109448</t>
+          <t>110140</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36853</t>
+          <t>36163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60963</t>
+          <t>61360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>40973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>64271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>95641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87523</t>
+          <t>87652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111185</t>
+          <t>110370</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59785</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76698</t>
+          <t>76373</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>153509</t>
+          <t>152735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182188</t>
+          <t>182755</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>29039</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50082</t>
+          <t>50705</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45500</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72480</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11935</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94503</t>
+          <t>95874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119726</t>
+          <t>121304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48352</t>
+          <t>48524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68468</t>
+          <t>68887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150996</t>
+          <t>149597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>183348</t>
+          <t>181861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25162</t>
+          <t>24907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48199</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>18703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37805</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>50883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78126</t>
+          <t>78971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38655</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>35177</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58366</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,75%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22478</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16240</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33896</t>
+          <t>34050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45674</t>
+          <t>44781</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61969</t>
+          <t>62069</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32416</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46663</t>
+          <t>46227</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81220</t>
+          <t>81264</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>104436</t>
+          <t>103860</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6154</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>36613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77130</t>
+          <t>77025</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97891</t>
+          <t>97909</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>32445</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>47126</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114652</t>
+          <t>114282</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>139751</t>
+          <t>139709</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>35728</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19258</t>
+          <t>18952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49509</t>
+          <t>49108</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18967</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>15874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>34423</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>90970</t>
+          <t>90842</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>122003</t>
+          <t>121957</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54587</t>
+          <t>55110</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79816</t>
+          <t>80018</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>154141</t>
+          <t>150385</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192162</t>
+          <t>192058</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>62735</t>
+          <t>63960</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>92515</t>
+          <t>93114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44907</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68749</t>
+          <t>68738</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>115792</t>
+          <t>116753</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>154561</t>
+          <t>155445</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38932</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>65697</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49321</t>
+          <t>48779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73273</t>
+          <t>72346</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106690</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>49691</t>
+          <t>49045</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>43415</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72706</t>
+          <t>72579</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>175370</t>
+          <t>176358</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>211663</t>
+          <t>211647</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110495</t>
+          <t>109843</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>136897</t>
+          <t>136576</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>292960</t>
+          <t>296351</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>338690</t>
+          <t>338400</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>69601</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>101372</t>
+          <t>101312</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>31642</t>
+          <t>32797</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>55740</t>
+          <t>57271</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109488</t>
+          <t>109930</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>150115</t>
+          <t>150242</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>563792</t>
+          <t>563606</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>639292</t>
+          <t>636307</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>317656</t>
+          <t>318528</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>374861</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>898567</t>
+          <t>900423</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>996624</t>
+          <t>995130</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>472035</t>
+          <t>474465</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>546227</t>
+          <t>545618</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>322346</t>
+          <t>319714</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>378871</t>
+          <t>375955</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>813423</t>
+          <t>810310</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>907251</t>
+          <t>905506</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>243911</t>
+          <t>243775</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>304309</t>
+          <t>305297</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>145970</t>
+          <t>142891</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>189219</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>396724</t>
+          <t>405834</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>475745</t>
+          <t>484202</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2012 (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>20611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>15863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>39772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19340</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39005</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>64713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>94077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61437</t>
+          <t>62763</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86198</t>
+          <t>86413</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49131</t>
+          <t>49237</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70361</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118256</t>
+          <t>118219</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149460</t>
+          <t>149326</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>16381</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>34440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30822</t>
+          <t>31086</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59171</t>
+          <t>59519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66182</t>
+          <t>65664</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96562</t>
+          <t>96681</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48663</t>
+          <t>50356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74967</t>
+          <t>75586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>124811</t>
+          <t>123031</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>162259</t>
+          <t>162804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86143</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115920</t>
+          <t>116117</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82995</t>
+          <t>80092</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150164</t>
+          <t>149184</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189473</t>
+          <t>189661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,08%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>25244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46962</t>
+          <t>45721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32692</t>
+          <t>33332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55497</t>
+          <t>56399</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,41%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43845</t>
+          <t>44383</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66720</t>
+          <t>66719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42679</t>
+          <t>41541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61858</t>
+          <t>62235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92552</t>
+          <t>92490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120944</t>
+          <t>122461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26580</t>
+          <t>27109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47096</t>
+          <t>46653</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17579</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35539</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49824</t>
+          <t>49779</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75599</t>
+          <t>75950</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>52046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35440</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52796</t>
+          <t>53539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82904</t>
+          <t>82755</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>42112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65242</t>
+          <t>65951</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28012</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>49056</t>
+          <t>46851</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74157</t>
+          <t>74253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107489</t>
+          <t>108046</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25350</t>
+          <t>24753</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46782</t>
+          <t>46650</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51702</t>
+          <t>50653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61092</t>
+          <t>61530</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>91010</t>
+          <t>92665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16199</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11961</t>
+          <t>12599</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>23848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56434</t>
+          <t>57182</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31574</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>47660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>72913</t>
+          <t>73484</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99300</t>
+          <t>99525</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25320</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45510</t>
+          <t>43526</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14255</t>
+          <t>14154</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>30318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>43262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67405</t>
+          <t>68772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,14%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>25698</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31850</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>46800</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32784</t>
+          <t>32562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>48376</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67586</t>
+          <t>67036</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>92082</t>
+          <t>91071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>60,46%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>37761</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28241</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37956</t>
+          <t>37857</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>61209</t>
+          <t>60927</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45986</t>
+          <t>47064</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75050</t>
+          <t>75533</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47970</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>77872</t>
+          <t>78848</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113350</t>
+          <t>113256</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121889</t>
+          <t>118777</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>156727</t>
+          <t>153217</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>81765</t>
+          <t>81439</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>111374</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>208720</t>
+          <t>211467</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>255523</t>
+          <t>254917</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>67623</t>
+          <t>68802</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>99261</t>
+          <t>100254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>49806</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77415</t>
+          <t>77348</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>125998</t>
+          <t>126559</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>167196</t>
+          <t>167970</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50995</t>
+          <t>51709</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18969</t>
+          <t>18610</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39312</t>
+          <t>38057</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51648</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>84120</t>
+          <t>82802</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>142702</t>
+          <t>142516</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>177570</t>
+          <t>180204</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>102995</t>
+          <t>104858</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>132644</t>
+          <t>134582</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>256518</t>
+          <t>255770</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>303024</t>
+          <t>302737</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>76676</t>
+          <t>74761</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>108090</t>
+          <t>108089</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>48268</t>
+          <t>47074</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>75514</t>
+          <t>74899</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>132201</t>
+          <t>130434</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>174523</t>
+          <t>175412</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,14%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>209175</t>
+          <t>208335</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>265597</t>
+          <t>268875</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>117604</t>
+          <t>117588</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>163261</t>
+          <t>162324</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>338066</t>
+          <t>338507</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>410611</t>
+          <t>410605</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>585405</t>
+          <t>585344</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>663028</t>
+          <t>664426</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>446884</t>
+          <t>442571</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>508856</t>
+          <t>508273</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1047935</t>
+          <t>1047411</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1146631</t>
+          <t>1147182</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>448098</t>
+          <t>447789</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>518478</t>
+          <t>524096</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>326717</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>389445</t>
+          <t>391436</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>797125</t>
+          <t>794606</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>897632</t>
+          <t>892970</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9217,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016</t>
+          <t>Población según si su médico le ha aconsejado que deje de fumar en 2016 (tasa de respuesta: 97,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>14519</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32307</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21496</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>41805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23414</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42937</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25585</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37617</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63422</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>38454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>39343</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55454</t>
+          <t>55510</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83257</t>
+          <t>83783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109892</t>
+          <t>110654</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>62,09%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138645</t>
+          <t>138556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>163488</t>
+          <t>164281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80142</t>
+          <t>79269</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>102585</t>
+          <t>101750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>226129</t>
+          <t>223706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>259563</t>
+          <t>258862</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34525</t>
+          <t>34203</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56810</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>31489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>53921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71388</t>
+          <t>71523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103186</t>
+          <t>104087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58239</t>
+          <t>58615</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30043</t>
+          <t>30220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47273</t>
+          <t>47698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75337</t>
+          <t>74484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101447</t>
+          <t>100214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>34333</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54075</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30698</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>47856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69331</t>
+          <t>70537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95615</t>
+          <t>96799</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20006</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39383</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17441</t>
+          <t>18030</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28533</t>
+          <t>29045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>51418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>39739</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>62479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34650</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55769</t>
+          <t>56152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81826</t>
+          <t>80851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113470</t>
+          <t>113211</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>47996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70148</t>
+          <t>71067</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>40703</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62553</t>
+          <t>62645</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>93434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126660</t>
+          <t>125796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -11236,97 +11236,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1780</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>39559</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31591</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>83818</t>
+          <t>84571</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,69%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21574</t>
+          <t>22414</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>39544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51085</t>
+          <t>50332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73765</t>
+          <t>72971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>24476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>12404</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30687</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>39972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60244</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>48993</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>62960</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>96108</t>
+          <t>95057</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119263</t>
+          <t>119097</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14181</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>30493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17108</t>
+          <t>16441</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>43396</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>63930</t>
+          <t>62659</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93573</t>
+          <t>92295</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49360</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73838</t>
+          <t>75099</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120379</t>
+          <t>120441</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>157722</t>
+          <t>159352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55550</t>
+          <t>56440</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>32750</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55571</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>70460</t>
+          <t>71711</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>105107</t>
+          <t>105319</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62634</t>
+          <t>63146</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92363</t>
+          <t>92324</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55023</t>
+          <t>55443</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80271</t>
+          <t>80123</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>125322</t>
+          <t>123803</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>164521</t>
+          <t>162654</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27787</t>
+          <t>27662</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>39134</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>32130</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>59598</t>
+          <t>58211</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>126894</t>
+          <t>126803</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>160039</t>
+          <t>161081</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>92355</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>119751</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>229988</t>
+          <t>228702</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>272607</t>
+          <t>270812</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>74729</t>
+          <t>74189</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>107652</t>
+          <t>105507</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>52328</t>
+          <t>51855</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>79117</t>
+          <t>78633</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>133466</t>
+          <t>133400</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>174444</t>
+          <t>173790</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>152920</t>
+          <t>151377</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>203002</t>
+          <t>202916</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13075,12 +13075,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>104927</t>
+          <t>101245</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>143298</t>
+          <t>141787</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>268494</t>
+          <t>265747</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>338442</t>
+          <t>332982</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>533918</t>
+          <t>536944</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>604550</t>
+          <t>607611</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>398215</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>456641</t>
+          <t>454198</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,12 +13223,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>950462</t>
+          <t>946894</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1044514</t>
+          <t>1038487</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>384577</t>
+          <t>382325</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>449395</t>
+          <t>450863</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>324188</t>
+          <t>322678</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>380648</t>
+          <t>380689</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>725189</t>
+          <t>728954</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>814550</t>
+          <t>816917</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P24C-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68398</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28693</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47151</t>
+          <t>46523</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82555</t>
+          <t>81717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>110961</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,13%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43385</t>
+          <t>42068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37016</t>
+          <t>37318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47108</t>
+          <t>48402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72854</t>
+          <t>74343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,04%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16576</t>
+          <t>15692</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20731</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42604</t>
+          <t>42542</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75099</t>
+          <t>75278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>103593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58504</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120337</t>
+          <t>120308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>155530</t>
+          <t>155584</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>42470</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68093</t>
+          <t>67694</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>29226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49129</t>
+          <t>49838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>77613</t>
+          <t>78185</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>110140</t>
+          <t>110015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>35628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61360</t>
+          <t>60750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21707</t>
+          <t>22566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64271</t>
+          <t>64679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95641</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87652</t>
+          <t>87195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>110370</t>
+          <t>110488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59038</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76373</t>
+          <t>76417</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>152735</t>
+          <t>152605</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>182755</t>
+          <t>182198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,06%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>28438</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50705</t>
+          <t>51335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28653</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>46568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>73210</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9104</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>26437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>95874</t>
+          <t>94538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>119262</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>48524</t>
+          <t>48081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68887</t>
+          <t>68724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>149597</t>
+          <t>150359</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>181861</t>
+          <t>182160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>19338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>37371</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50883</t>
+          <t>48947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78971</t>
+          <t>78177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>59825</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>23980</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>16002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>34262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44781</t>
+          <t>44120</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>62069</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>32291</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46227</t>
+          <t>46386</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>80917</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>103860</t>
+          <t>103896</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,22%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>23120</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>17944</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18501</t>
+          <t>17940</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36613</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77025</t>
+          <t>77062</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>97909</t>
+          <t>97578</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>32204</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>46965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114282</t>
+          <t>113377</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>139709</t>
+          <t>138454</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17690</t>
+          <t>17826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>35728</t>
+          <t>35854</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18952</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>49108</t>
+          <t>49300</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18967</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>15672</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34423</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>90842</t>
+          <t>91842</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121957</t>
+          <t>121838</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>80018</t>
+          <t>78922</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>48,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>150385</t>
+          <t>154213</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192058</t>
+          <t>193096</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>63960</t>
+          <t>63628</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93114</t>
+          <t>93826</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>45978</t>
+          <t>44483</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>68738</t>
+          <t>68797</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>116753</t>
+          <t>116875</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>155445</t>
+          <t>153807</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39503</t>
+          <t>39404</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65697</t>
+          <t>65669</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>27571</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>48671</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72346</t>
+          <t>72467</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>105999</t>
+          <t>107354</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,09%</t>
         </is>
       </c>
     </row>
@@ -3924,12 +3924,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>26515</t>
+          <t>26275</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>49045</t>
+          <t>50350</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>28451</t>
+          <t>28735</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43415</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>72579</t>
+          <t>73148</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -4037,12 +4037,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>176358</t>
+          <t>175765</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>211647</t>
+          <t>211990</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>109843</t>
+          <t>110565</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>136576</t>
+          <t>136134</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>296351</t>
+          <t>294647</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>338400</t>
+          <t>337922</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,32%</t>
         </is>
       </c>
     </row>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>69589</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>101312</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>57271</t>
+          <t>56623</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109930</t>
+          <t>110977</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>150242</t>
+          <t>148397</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>563606</t>
+          <t>565477</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>636307</t>
+          <t>633093</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>318528</t>
+          <t>319953</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>378223</t>
+          <t>377136</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>900423</t>
+          <t>899861</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>995130</t>
+          <t>994652</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>474465</t>
+          <t>472753</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>545618</t>
+          <t>546653</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>319714</t>
+          <t>317181</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>375955</t>
+          <t>374681</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>810310</t>
+          <t>810633</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>905506</t>
+          <t>906603</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>243775</t>
+          <t>244946</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>305297</t>
+          <t>302760</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>142891</t>
+          <t>144247</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>189219</t>
+          <t>190601</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>405834</t>
+          <t>402578</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>484202</t>
+          <t>480266</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -5072,12 +5072,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>12814</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32218</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5157,12 +5157,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39772</t>
+          <t>40152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>19353</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38696</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64713</t>
+          <t>66618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94077</t>
+          <t>95879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5270,12 +5270,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62763</t>
+          <t>61665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>86413</t>
+          <t>85959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49237</t>
+          <t>49816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69876</t>
+          <t>70564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118219</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149326</t>
+          <t>148180</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16381</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34440</t>
+          <t>33455</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13762</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31086</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34031</t>
+          <t>33528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59519</t>
+          <t>57838</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65664</t>
+          <t>67146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>96681</t>
+          <t>96547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50356</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75586</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>123031</t>
+          <t>123597</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>162804</t>
+          <t>163386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85399</t>
+          <t>86332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116117</t>
+          <t>117040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80092</t>
+          <t>81101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149184</t>
+          <t>148409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>189661</t>
+          <t>189714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25244</t>
+          <t>26185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45721</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>15775</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6054,12 +6054,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>33332</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>56399</t>
+          <t>55961</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6097,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>44415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>66694</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62235</t>
+          <t>60619</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6167,12 +6167,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92490</t>
+          <t>93179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122461</t>
+          <t>122311</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,28%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46653</t>
+          <t>47340</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>36298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>49779</t>
+          <t>48682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75950</t>
+          <t>74966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,11%</t>
         </is>
       </c>
     </row>
@@ -6440,12 +6440,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29773</t>
+          <t>30507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52046</t>
+          <t>53382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>35393</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53539</t>
+          <t>53113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82755</t>
+          <t>81459</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42112</t>
+          <t>41140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>65951</t>
+          <t>66086</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>27777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46851</t>
+          <t>47852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6623,12 +6623,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>74253</t>
+          <t>75502</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108046</t>
+          <t>107399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6638,12 +6638,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,9%</t>
         </is>
       </c>
     </row>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24753</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46650</t>
+          <t>45652</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30280</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50653</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>61530</t>
+          <t>62155</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92665</t>
+          <t>92834</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6751,12 +6751,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,67%</t>
         </is>
       </c>
     </row>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16492</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12599</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>25275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -7009,12 +7009,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37473</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57182</t>
+          <t>57159</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47660</t>
+          <t>48381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73484</t>
+          <t>73069</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>99525</t>
+          <t>98167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,01%</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25383</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43526</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7157,12 +7157,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14154</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30318</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43262</t>
+          <t>44004</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68772</t>
+          <t>68008</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,65%</t>
         </is>
       </c>
     </row>
@@ -7352,12 +7352,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12489</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14960</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31863</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>29648</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46800</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32562</t>
+          <t>33313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>48973</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>66626</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91071</t>
+          <t>92199</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -7578,12 +7578,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>21564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13784</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>27502</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37857</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60927</t>
+          <t>62552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -7808,12 +7808,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>47064</t>
+          <t>46867</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>75533</t>
+          <t>74316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>25747</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78848</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>113256</t>
+          <t>114624</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7893,12 +7893,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -7921,12 +7921,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118777</t>
+          <t>120018</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153217</t>
+          <t>153783</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>81439</t>
+          <t>82160</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>112814</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>211467</t>
+          <t>209632</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>254917</t>
+          <t>254712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8006,12 +8006,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,65%</t>
         </is>
       </c>
     </row>
@@ -8034,12 +8034,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>68634</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100254</t>
+          <t>99702</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49806</t>
+          <t>49759</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77348</t>
+          <t>76438</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>126559</t>
+          <t>126646</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>167970</t>
+          <t>167134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8119,12 +8119,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51709</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8299,12 +8299,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18610</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>38057</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8314,12 +8314,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8334,12 +8334,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>82802</t>
+          <t>83738</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8349,12 +8349,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -8377,12 +8377,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>142516</t>
+          <t>143188</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>180204</t>
+          <t>178867</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8392,12 +8392,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>104858</t>
+          <t>104452</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>134582</t>
+          <t>132394</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>255770</t>
+          <t>257548</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>302737</t>
+          <t>302369</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8462,12 +8462,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -8490,12 +8490,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>74761</t>
+          <t>74923</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>108089</t>
+          <t>109023</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>47887</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>74899</t>
+          <t>75020</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>130434</t>
+          <t>132554</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>175412</t>
+          <t>175158</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -8720,12 +8720,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>208335</t>
+          <t>207140</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>268875</t>
+          <t>267054</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>117588</t>
+          <t>117199</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>162324</t>
+          <t>162056</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>338507</t>
+          <t>338756</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>410605</t>
+          <t>412082</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8805,12 +8805,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,77%</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8833,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>585344</t>
+          <t>582646</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>664426</t>
+          <t>662657</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8848,12 +8848,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8868,12 +8868,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>442571</t>
+          <t>445468</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>508273</t>
+          <t>509000</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8883,12 +8883,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1047411</t>
+          <t>1048377</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1147182</t>
+          <t>1150002</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -8946,12 +8946,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>447789</t>
+          <t>450037</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>524096</t>
+          <t>522206</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>326717</t>
+          <t>331626</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>391436</t>
+          <t>392608</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>794606</t>
+          <t>799820</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>892970</t>
+          <t>894166</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4118</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9482,12 +9482,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>20925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41805</t>
+          <t>42374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9497,12 +9497,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -9525,12 +9525,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23864</t>
+          <t>23555</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>44171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>25280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63527</t>
+          <t>64136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -9638,12 +9638,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59221</t>
+          <t>59949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39343</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55510</t>
+          <t>54822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83783</t>
+          <t>84234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>110654</t>
+          <t>111297</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,45%</t>
         </is>
       </c>
     </row>
@@ -9868,12 +9868,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9938,12 +9938,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28199</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9953,12 +9953,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>138556</t>
+          <t>135869</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164281</t>
+          <t>164415</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79269</t>
+          <t>78488</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101750</t>
+          <t>102526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>223706</t>
+          <t>225516</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258862</t>
+          <t>259570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10066,12 +10066,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34203</t>
+          <t>34260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>58745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53921</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71523</t>
+          <t>69511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104087</t>
+          <t>101855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8513</t>
+          <t>8989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>996</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10379,7 +10379,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>13859</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -10437,12 +10437,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38708</t>
+          <t>40170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58615</t>
+          <t>59382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>47688</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74484</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>100705</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>34026</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54562</t>
+          <t>52953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>30467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47856</t>
+          <t>47297</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>70537</t>
+          <t>71139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96799</t>
+          <t>96998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -10780,12 +10780,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20055</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>40224</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18030</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29045</t>
+          <t>28891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51418</t>
+          <t>52054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,15%</t>
         </is>
       </c>
     </row>
@@ -10893,12 +10893,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62479</t>
+          <t>63628</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34650</t>
+          <t>34957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56152</t>
+          <t>55578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>80851</t>
+          <t>80990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113211</t>
+          <t>111443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10978,12 +10978,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47996</t>
+          <t>46675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71067</t>
+          <t>70996</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40703</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>62645</t>
+          <t>62768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>93434</t>
+          <t>94868</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>125796</t>
+          <t>126501</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39559</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>56140</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11384,12 +11384,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>17046</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>32080</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11399,12 +11399,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11419,12 +11419,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>61932</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84571</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11434,12 +11434,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,37%</t>
         </is>
       </c>
     </row>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>40071</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11497,12 +11497,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>23720</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38696</t>
+          <t>38754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11532,12 +11532,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>50332</t>
+          <t>50760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72971</t>
+          <t>72922</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11547,12 +11547,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,06%</t>
         </is>
       </c>
     </row>
@@ -11692,12 +11692,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>24606</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2624</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -11805,12 +11805,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39972</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59675</t>
+          <t>60267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11820,12 +11820,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11840,12 +11840,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48993</t>
+          <t>49218</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62960</t>
+          <t>62955</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>95057</t>
+          <t>95823</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>119097</t>
+          <t>119228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -11918,12 +11918,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13538</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30493</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11933,12 +11933,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11953,12 +11953,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11968,12 +11968,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>21839</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43396</t>
+          <t>42140</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12003,12 +12003,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -12148,12 +12148,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>62659</t>
+          <t>63769</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92295</t>
+          <t>93684</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12163,12 +12163,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12183,12 +12183,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49982</t>
+          <t>48789</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>75099</t>
+          <t>74331</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120441</t>
+          <t>119297</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159352</t>
+          <t>158488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -12261,12 +12261,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>31261</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>56440</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12276,12 +12276,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12296,12 +12296,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>56326</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12311,12 +12311,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>71711</t>
+          <t>68882</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>105319</t>
+          <t>102666</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>27,82%</t>
         </is>
       </c>
     </row>
@@ -12374,12 +12374,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63146</t>
+          <t>61186</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>92324</t>
+          <t>91945</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12409,12 +12409,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>55443</t>
+          <t>54641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80123</t>
+          <t>79819</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12424,12 +12424,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12444,12 +12444,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>123803</t>
+          <t>124849</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>162654</t>
+          <t>165329</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12459,12 +12459,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -12604,12 +12604,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12619,12 +12619,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12639,12 +12639,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18380</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>38584</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12654,12 +12654,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>32861</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>58211</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -12717,12 +12717,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>126803</t>
+          <t>127438</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>161081</t>
+          <t>159326</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12752,12 +12752,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>92355</t>
+          <t>92939</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>119751</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12767,12 +12767,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>228702</t>
+          <t>226416</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>270812</t>
+          <t>272177</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -12830,12 +12830,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>74189</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>105507</t>
+          <t>105458</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12865,12 +12865,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>51855</t>
+          <t>52295</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>78633</t>
+          <t>77979</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12880,12 +12880,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12900,12 +12900,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>133400</t>
+          <t>132586</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>173790</t>
+          <t>174160</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -13060,12 +13060,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>151377</t>
+          <t>151388</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>202916</t>
+          <t>204390</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13095,12 +13095,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>101245</t>
+          <t>104924</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>141787</t>
+          <t>144678</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13130,12 +13130,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>265747</t>
+          <t>267512</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>332982</t>
+          <t>332201</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13145,12 +13145,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -13173,12 +13173,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>536944</t>
+          <t>532492</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>607611</t>
+          <t>605891</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13208,12 +13208,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>396063</t>
+          <t>391254</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>454198</t>
+          <t>454237</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -13243,12 +13243,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>946894</t>
+          <t>950975</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1038487</t>
+          <t>1040076</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13258,12 +13258,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -13286,12 +13286,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>382325</t>
+          <t>379365</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>450863</t>
+          <t>448964</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13321,12 +13321,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>322678</t>
+          <t>321357</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>380689</t>
+          <t>381857</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13336,12 +13336,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>728954</t>
+          <t>725046</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>816917</t>
+          <t>814744</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,48%</t>
         </is>
       </c>
     </row>
